--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="43">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -25,49 +25,52 @@
     <t>ZONA</t>
   </si>
   <si>
+    <t>EN PROCESO DE VENTA</t>
+  </si>
+  <si>
+    <t>VENDIDOS CON PRECIO</t>
+  </si>
+  <si>
+    <t>PROMOS</t>
+  </si>
+  <si>
+    <t>CORTESÍAS</t>
+  </si>
+  <si>
+    <t>PRECIO $1</t>
+  </si>
+  <si>
+    <t>ABONOS VENDIDOS</t>
+  </si>
+  <si>
+    <t>ABONOS PROMOS</t>
+  </si>
+  <si>
+    <t>ABONOS CORTESÍAS</t>
+  </si>
+  <si>
+    <t>ABONOS PRECIO $1</t>
+  </si>
+  <si>
+    <t>PAQUETES</t>
+  </si>
+  <si>
+    <t>PAQUETES CORTESIAS</t>
+  </si>
+  <si>
+    <t>PAQUETES PRECIO $1</t>
+  </si>
+  <si>
+    <t>PROMOCIONES</t>
+  </si>
+  <si>
+    <t>BLOQUEOS</t>
+  </si>
+  <si>
     <t>AFORO</t>
   </si>
   <si>
-    <t>VENDIDOS</t>
-  </si>
-  <si>
-    <t>PROMOS</t>
-  </si>
-  <si>
-    <t>CORTESÍAS</t>
-  </si>
-  <si>
-    <t>PRECIO $1</t>
-  </si>
-  <si>
-    <t>ABONOS VENDIDOS</t>
-  </si>
-  <si>
-    <t>ABONOS PROMOS</t>
-  </si>
-  <si>
-    <t>ABONOS CORTESÍAS</t>
-  </si>
-  <si>
-    <t>ABONOS PRECIO $1</t>
-  </si>
-  <si>
-    <t>PAQUETES</t>
-  </si>
-  <si>
-    <t>PAQUETES CORTESIAS</t>
-  </si>
-  <si>
-    <t>PAQUETES PRECIO $1</t>
-  </si>
-  <si>
-    <t>BLOQUEOS</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>OCUPADOS</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -196,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -213,11 +216,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,11 +570,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="18" width="25" customWidth="1"/>
+    <col min="2" max="19" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -585,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -640,565 +652,598 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="7">
+        <v>50</v>
+      </c>
+      <c r="P6" s="7">
+        <v>1515</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>50</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1465</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="7">
+        <v>40</v>
+      </c>
+      <c r="P7" s="7">
+        <v>1516</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>40</v>
+      </c>
+      <c r="R7" s="7">
+        <v>1476</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="7">
+        <v>12</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="7">
+        <v>60</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="7">
+        <v>99</v>
+      </c>
+      <c r="P8" s="7">
+        <v>174</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>171</v>
+      </c>
+      <c r="R8" s="7">
+        <v>3</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="7">
+        <v>32</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="7">
+        <v>82</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="7">
+        <v>50</v>
+      </c>
+      <c r="P9" s="7">
+        <v>164</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>164</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="7">
         <v>21</v>
       </c>
-      <c r="B6" s="6">
-        <v>1515</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="6">
-        <v>50</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="6">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1465</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="6">
-        <v>1516</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="6">
+      <c r="H10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="7">
+        <v>160</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="7">
+        <v>169</v>
+      </c>
+      <c r="P10" s="7">
+        <v>360</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>350</v>
+      </c>
+      <c r="R10" s="7">
+        <v>10</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="7">
+        <v>53</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="7">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="7">
+        <v>755</v>
+      </c>
+      <c r="P11" s="7">
+        <v>1709</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>828</v>
+      </c>
+      <c r="R11" s="7">
+        <v>881</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="7">
+        <v>5</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="7">
+        <v>188</v>
+      </c>
+      <c r="P12" s="7">
+        <v>1853</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>193</v>
+      </c>
+      <c r="R12" s="7">
+        <v>1660</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="7">
+        <v>51</v>
+      </c>
+      <c r="P13" s="7">
+        <v>128</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>51</v>
+      </c>
+      <c r="R13" s="7">
+        <v>77</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" s="7">
+        <v>400</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R14" s="7">
+        <v>400</v>
+      </c>
+      <c r="S14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>1476</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="6">
-        <v>174</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6">
-        <v>12</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="6">
-        <v>60</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="6">
-        <v>99</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="6">
-        <v>171</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>3</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6">
-        <v>164</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="6">
-        <v>32</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="6">
-        <v>82</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="6">
-        <v>50</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="6">
-        <v>164</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
-        <v>360</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="6">
-        <v>21</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="6">
-        <v>160</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="6">
-        <v>169</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="6">
-        <v>350</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>10</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="6">
-        <v>1709</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="6">
-        <v>53</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="6">
-        <v>20</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="6">
-        <v>755</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="6">
-        <v>828</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>881</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="6">
-        <v>1853</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="6">
-        <v>5</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" s="6">
-        <v>188</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="6">
-        <v>193</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>1660</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="6">
-        <v>128</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6">
-        <v>51</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="6">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>77</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="6">
-        <v>400</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>400</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="7">
+        <v>41</v>
+      </c>
+      <c r="B15" s="9">
         <f>SUM(B6:B14)</f>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="9">
         <f>SUM(C6:C14)</f>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="9">
         <f>SUM(D6:D14)</f>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="9">
         <f>SUM(E6:E14)</f>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="9">
         <f>SUM(F6:F14)</f>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="9">
         <f>SUM(G6:G14)</f>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <f>SUM(H6:H14)</f>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="9">
         <f>SUM(I6:I14)</f>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="9">
         <f>SUM(J6:J14)</f>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="9">
         <f>SUM(K6:K14)</f>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="9">
         <f>SUM(L6:L14)</f>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="9">
         <f>SUM(M6:M14)</f>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="9">
         <f>SUM(N6:N14)</f>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="9">
         <f>SUM(O6:O14)</f>
       </c>
-      <c r="P15" s="7">
+      <c r="P15" s="9">
         <f>SUM(P6:P14)</f>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q15" s="9">
         <f>SUM(Q6:Q14)</f>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>41</v>
+      <c r="R15" s="9">
+        <f>SUM(R6:R14)</f>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>3.30%</t>
+    <t>4.09%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
@@ -94,15 +94,12 @@
     <t>Oro</t>
   </si>
   <si>
-    <t>98.28%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Palcos Dorados</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Palcos Morados</t>
   </si>
   <si>
@@ -112,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>48.45%</t>
+    <t>51.20%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>10.42%</t>
+    <t>12.90%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -136,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>23.62%</t>
+    <t>25.00%</t>
   </si>
 </sst>
 </file>
@@ -648,14 +645,14 @@
       <c r="B6" s="6">
         <v>1515</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
+      <c r="C6" s="6">
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
+      <c r="E6" s="6">
+        <v>8</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -688,10 +685,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Q6" s="6">
-        <v>1465</v>
+        <v>1453</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -794,16 +791,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>171</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>3</v>
+        <v>174</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -862,12 +859,12 @@
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
         <v>360</v>
@@ -918,24 +915,24 @@
         <v>10</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>1709</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
+      <c r="C11" s="6">
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>39</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -962,36 +959,36 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="Q11" s="6">
-        <v>881</v>
+        <v>834</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>1853</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
+      <c r="C12" s="6">
+        <v>9</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
+      <c r="E12" s="6">
+        <v>33</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1018,24 +1015,24 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="Q12" s="6">
-        <v>1660</v>
+        <v>1614</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6">
         <v>128</v>
@@ -1086,12 +1083,12 @@
         <v>77</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6">
         <v>400</v>
@@ -1142,12 +1139,12 @@
         <v>400</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="7">
         <f>SUM(B6:B14)</f>
@@ -1198,7 +1195,7 @@
         <f>SUM(Q6:Q14)</f>
       </c>
       <c r="R15" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>4.09%</t>
+    <t>13.40%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>2.64%</t>
+    <t>5.67%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>51.20%</t>
+    <t>87.42%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>12.90%</t>
+    <t>41.18%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>25.00%</t>
+    <t>42.01%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -685,10 +685,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="Q6" s="6">
-        <v>1453</v>
+        <v>1312</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -701,8 +701,8 @@
       <c r="B7" s="6">
         <v>1516</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+      <c r="C7" s="6">
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -741,10 +741,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="Q7" s="6">
-        <v>1476</v>
+        <v>1430</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,25 +926,25 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>10</v>
+        <v>617</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -959,16 +959,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>753</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
+        <v>749</v>
+      </c>
+      <c r="O11" s="6">
+        <v>5</v>
       </c>
       <c r="P11" s="6">
-        <v>875</v>
+        <v>1494</v>
       </c>
       <c r="Q11" s="6">
-        <v>834</v>
+        <v>215</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,13 +982,13 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>9</v>
+        <v>517</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1017,14 +1017,14 @@
       <c r="N12" s="6">
         <v>192</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
+      <c r="O12" s="6">
+        <v>10</v>
       </c>
       <c r="P12" s="6">
-        <v>239</v>
+        <v>763</v>
       </c>
       <c r="Q12" s="6">
-        <v>1614</v>
+        <v>1090</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>13.40%</t>
+    <t>20.86%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>5.67%</t>
+    <t>7.65%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>87.42%</t>
+    <t>98.19%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>41.18%</t>
+    <t>71.99%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>42.01%</t>
+    <t>53.50%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -681,14 +681,14 @@
       <c r="N6" s="6">
         <v>50</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>8</v>
       </c>
       <c r="P6" s="6">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="Q6" s="6">
-        <v>1312</v>
+        <v>1199</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,7 +702,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -741,10 +741,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="6">
-        <v>1430</v>
+        <v>1400</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,13 +926,13 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>617</v>
+        <v>795</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -962,13 +962,13 @@
         <v>749</v>
       </c>
       <c r="O11" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P11" s="6">
-        <v>1494</v>
+        <v>1678</v>
       </c>
       <c r="Q11" s="6">
-        <v>215</v>
+        <v>31</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,13 +982,13 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>517</v>
+        <v>1069</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1015,16 +1015,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O12" s="6">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P12" s="6">
-        <v>763</v>
+        <v>1334</v>
       </c>
       <c r="Q12" s="6">
-        <v>1090</v>
+        <v>519</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>20.86%</t>
+    <t>24.69%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>7.65%</t>
+    <t>8.31%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>98.19%</t>
+    <t>98.83%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>71.99%</t>
+    <t>82.35%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>53.50%</t>
+    <t>56.96%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>250</v>
+        <v>316</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -681,14 +681,14 @@
       <c r="N6" s="6">
         <v>50</v>
       </c>
-      <c r="O6" s="6">
-        <v>8</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>316</v>
+        <v>374</v>
       </c>
       <c r="Q6" s="6">
-        <v>1199</v>
+        <v>1141</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,7 +702,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -741,10 +741,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="Q7" s="6">
-        <v>1400</v>
+        <v>1390</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,7 +926,7 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -962,13 +962,13 @@
         <v>749</v>
       </c>
       <c r="O11" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>1678</v>
+        <v>1689</v>
       </c>
       <c r="Q11" s="6">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,7 +982,7 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1069</v>
+        <v>1284</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1018,13 +1018,13 @@
         <v>190</v>
       </c>
       <c r="O12" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="P12" s="6">
-        <v>1334</v>
+        <v>1526</v>
       </c>
       <c r="Q12" s="6">
-        <v>519</v>
+        <v>327</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>24.69%</t>
+    <t>29.44%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>8.31%</t>
+    <t>10.16%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>98.83%</t>
+    <t>98.89%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>82.35%</t>
+    <t>89.80%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>56.96%</t>
+    <t>60.02%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -681,14 +681,14 @@
       <c r="N6" s="6">
         <v>50</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>374</v>
+        <v>446</v>
       </c>
       <c r="Q6" s="6">
-        <v>1141</v>
+        <v>1069</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,7 +702,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -737,14 +737,14 @@
       <c r="N7" s="6">
         <v>40</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>2</v>
       </c>
       <c r="P7" s="6">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="Q7" s="6">
-        <v>1390</v>
+        <v>1362</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,7 +926,7 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="Q11" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,7 +982,7 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1284</v>
+        <v>1412</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1018,13 +1018,13 @@
         <v>190</v>
       </c>
       <c r="O12" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P12" s="6">
-        <v>1526</v>
+        <v>1664</v>
       </c>
       <c r="Q12" s="6">
-        <v>327</v>
+        <v>189</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>29.44%</t>
+    <t>47.39%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>10.16%</t>
+    <t>32.26%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>98.89%</t>
+    <t>99.24%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>89.80%</t>
+    <t>95.95%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>60.02%</t>
+    <t>69.32%</t>
   </si>
 </sst>
 </file>
@@ -646,13 +646,13 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>384</v>
+        <v>513</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -679,16 +679,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="O6" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P6" s="6">
-        <v>446</v>
+        <v>718</v>
       </c>
       <c r="Q6" s="6">
-        <v>1069</v>
+        <v>797</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,13 +702,13 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>115</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -735,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>40</v>
-      </c>
-      <c r="O7" s="6">
-        <v>2</v>
+        <v>196</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>154</v>
+        <v>489</v>
       </c>
       <c r="Q7" s="6">
-        <v>1362</v>
+        <v>1027</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,13 +926,13 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -959,16 +959,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>749</v>
+        <v>665</v>
       </c>
       <c r="O11" s="6">
         <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>1690</v>
+        <v>1696</v>
       </c>
       <c r="Q11" s="6">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,13 +982,13 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1412</v>
+        <v>1527</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1015,16 +1015,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>190</v>
-      </c>
-      <c r="O12" s="6">
-        <v>12</v>
+        <v>130</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>1664</v>
+        <v>1778</v>
       </c>
       <c r="Q12" s="6">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>47.39%</t>
+    <t>52.67%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>32.26%</t>
+    <t>37.27%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>99.24%</t>
+    <t>99.30%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>95.95%</t>
+    <t>96.49%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>69.32%</t>
+    <t>71.45%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>513</v>
+        <v>609</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -679,16 +679,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="O6" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P6" s="6">
-        <v>718</v>
+        <v>798</v>
       </c>
       <c r="Q6" s="6">
-        <v>797</v>
+        <v>717</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,7 +702,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -737,14 +737,14 @@
       <c r="N7" s="6">
         <v>196</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>6</v>
       </c>
       <c r="P7" s="6">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="Q7" s="6">
-        <v>1027</v>
+        <v>951</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -826,7 +826,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
@@ -847,7 +847,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
@@ -882,7 +882,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
@@ -903,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
@@ -926,13 +926,13 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -959,16 +959,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="O11" s="6">
         <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="Q11" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,7 +982,7 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1017,14 +1017,14 @@
       <c r="N12" s="6">
         <v>130</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
+      <c r="O12" s="6">
+        <v>1</v>
       </c>
       <c r="P12" s="6">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="Q12" s="6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>52.67%</t>
+    <t>80.07%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>37.27%</t>
+    <t>50.86%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>99.30%</t>
+    <t>99.94%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>96.49%</t>
+    <t>98.87%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>71.45%</t>
+    <t>80.10%</t>
   </si>
 </sst>
 </file>
@@ -646,13 +646,13 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>609</v>
+        <v>909</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -679,16 +679,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>73</v>
-      </c>
-      <c r="O6" s="6">
-        <v>8</v>
+        <v>188</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>798</v>
+        <v>1213</v>
       </c>
       <c r="Q6" s="6">
-        <v>717</v>
+        <v>302</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,7 +702,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>248</v>
+        <v>458</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -738,13 +738,13 @@
         <v>196</v>
       </c>
       <c r="O7" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P7" s="6">
-        <v>565</v>
+        <v>771</v>
       </c>
       <c r="Q7" s="6">
-        <v>951</v>
+        <v>745</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,7 +926,7 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>817</v>
+        <v>830</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -959,16 +959,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="O11" s="6">
         <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>1697</v>
+        <v>1708</v>
       </c>
       <c r="Q11" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -982,13 +982,13 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1536</v>
+        <v>1577</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1015,16 +1015,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>130</v>
-      </c>
-      <c r="O12" s="6">
-        <v>1</v>
+        <v>121</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>1788</v>
+        <v>1832</v>
       </c>
       <c r="Q12" s="6">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1071,10 +1071,10 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>51</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="O13" s="6">
+        <v>15</v>
       </c>
       <c r="P13" s="6">
         <v>51</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>80.07%</t>
+    <t>89.83%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>50.86%</t>
+    <t>57.19%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -109,13 +109,10 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>99.94%</t>
-  </si>
-  <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>98.87%</t>
+    <t>98.97%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -133,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>80.10%</t>
+    <t>83.26%</t>
   </si>
 </sst>
 </file>
@@ -646,13 +643,13 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>909</v>
+        <v>1044</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -685,10 +682,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>1213</v>
+        <v>1361</v>
       </c>
       <c r="Q6" s="6">
-        <v>302</v>
+        <v>154</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,13 +699,13 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>458</v>
+        <v>554</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -735,16 +732,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="O7" s="6">
         <v>2</v>
       </c>
       <c r="P7" s="6">
-        <v>771</v>
+        <v>867</v>
       </c>
       <c r="Q7" s="6">
-        <v>745</v>
+        <v>649</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -926,13 +923,13 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -959,36 +956,36 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="O11" s="6">
         <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>1708</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>1</v>
+        <v>1709</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1015,24 +1012,24 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="Q12" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>128</v>
@@ -1055,8 +1052,8 @@
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
+      <c r="I13" s="6">
+        <v>15</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1073,8 +1070,8 @@
       <c r="N13" s="6">
         <v>36</v>
       </c>
-      <c r="O13" s="6">
-        <v>15</v>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
         <v>51</v>
@@ -1083,12 +1080,12 @@
         <v>77</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="6">
         <v>400</v>
@@ -1139,12 +1136,12 @@
         <v>400</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="7">
         <f>SUM(B6:B14)</f>
@@ -1195,7 +1192,7 @@
         <f>SUM(Q6:Q14)</f>
       </c>
       <c r="R15" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>89.83%</t>
+    <t>95.51%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>57.19%</t>
+    <t>64.38%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -112,7 +112,7 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>98.97%</t>
+    <t>99.46%</t>
   </si>
   <si>
     <t>Suite Premier</t>
@@ -130,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>83.26%</t>
+    <t>85.87%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>1044</v>
+        <v>1123</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -678,14 +678,14 @@
       <c r="N6" s="6">
         <v>188</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>7</v>
       </c>
       <c r="P6" s="6">
-        <v>1361</v>
+        <v>1447</v>
       </c>
       <c r="Q6" s="6">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +699,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>554</v>
+        <v>662</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -735,13 +735,13 @@
         <v>176</v>
       </c>
       <c r="O7" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" s="6">
-        <v>867</v>
+        <v>976</v>
       </c>
       <c r="Q7" s="6">
-        <v>649</v>
+        <v>540</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -929,7 +929,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -941,7 +941,7 @@
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -979,7 +979,7 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1018,10 +1018,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>1834</v>
+        <v>1843</v>
       </c>
       <c r="Q12" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>95.51%</t>
+    <t>98.09%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>64.38%</t>
+    <t>77.97%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -112,9 +112,6 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>99.46%</t>
-  </si>
-  <si>
     <t>Suite Premier</t>
   </si>
   <si>
@@ -130,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>85.87%</t>
+    <t>89.13%</t>
   </si>
 </sst>
 </file>
@@ -643,13 +640,13 @@
         <v>1515</v>
       </c>
       <c r="C6" s="6">
-        <v>1123</v>
+        <v>1167</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -676,16 +673,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="O6" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P6" s="6">
-        <v>1447</v>
+        <v>1486</v>
       </c>
       <c r="Q6" s="6">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +696,7 @@
         <v>1516</v>
       </c>
       <c r="C7" s="6">
-        <v>662</v>
+        <v>870</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -735,13 +732,13 @@
         <v>176</v>
       </c>
       <c r="O7" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P7" s="6">
-        <v>976</v>
+        <v>1182</v>
       </c>
       <c r="Q7" s="6">
-        <v>540</v>
+        <v>334</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -760,8 +757,8 @@
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>20</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -788,7 +785,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
@@ -885,7 +882,7 @@
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -900,7 +897,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
@@ -923,13 +920,13 @@
         <v>1709</v>
       </c>
       <c r="C11" s="6">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -941,7 +938,7 @@
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -956,10 +953,10 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>644</v>
+        <v>598</v>
       </c>
       <c r="O11" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" s="6">
         <v>1709</v>
@@ -979,13 +976,13 @@
         <v>1853</v>
       </c>
       <c r="C12" s="6">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1012,24 +1009,24 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>127</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
+        <v>120</v>
+      </c>
+      <c r="O12" s="6">
+        <v>1</v>
       </c>
       <c r="P12" s="6">
-        <v>1843</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>10</v>
+        <v>1853</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>128</v>
@@ -1080,12 +1077,12 @@
         <v>77</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6">
         <v>400</v>
@@ -1136,12 +1133,12 @@
         <v>400</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="7">
         <f>SUM(B6:B14)</f>
@@ -1192,7 +1189,7 @@
         <f>SUM(Q6:Q14)</f>
       </c>
       <c r="R15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -76,19 +76,25 @@
     <t>% OCUPACIÓN</t>
   </si>
   <si>
+    <t>Grada Sol</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.82%</t>
+  </si>
+  <si>
     <t>Jardin Derecho</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>98.09%</t>
+    <t>99.27%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>77.97%</t>
+    <t>95.84%</t>
   </si>
   <si>
     <t>Oro</t>
@@ -127,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>89.13%</t>
+    <t>54.83%</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -637,16 +643,16 @@
         <v>21</v>
       </c>
       <c r="B6" s="6">
-        <v>1515</v>
+        <v>5500</v>
       </c>
       <c r="C6" s="6">
-        <v>1167</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6">
-        <v>139</v>
+      <c r="E6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -672,17 +678,17 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6">
-        <v>178</v>
-      </c>
-      <c r="O6" s="6">
-        <v>2</v>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>1486</v>
+        <v>45</v>
       </c>
       <c r="Q6" s="6">
-        <v>29</v>
+        <v>5455</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -693,16 +699,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C7" s="6">
-        <v>870</v>
+        <v>1187</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -729,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>176</v>
-      </c>
-      <c r="O7" s="6">
-        <v>1</v>
+        <v>143</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1182</v>
+        <v>1504</v>
       </c>
       <c r="Q7" s="6">
-        <v>334</v>
+        <v>11</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -749,28 +755,28 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>174</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
+        <v>1516</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1141</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="6">
-        <v>12</v>
+      <c r="G8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="6">
-        <v>60</v>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -785,16 +791,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>82</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+        <v>166</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1</v>
       </c>
       <c r="P8" s="6">
-        <v>174</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>22</v>
+        <v>1453</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>63</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -805,7 +811,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>22</v>
@@ -813,103 +819,103 @@
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+      <c r="E9" s="6">
+        <v>20</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="6">
+        <v>60</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="6">
         <v>82</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="6">
-        <v>40</v>
-      </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6">
+        <v>164</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6">
+        <v>42</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="6">
+        <v>82</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="6">
+        <v>40</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="6">
+        <v>164</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B10" s="6">
-        <v>360</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="6">
-        <v>41</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="6">
-        <v>199</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="6">
-        <v>110</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="6">
-        <v>350</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>10</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -917,28 +923,28 @@
         <v>31</v>
       </c>
       <c r="B11" s="6">
-        <v>1709</v>
-      </c>
-      <c r="C11" s="6">
-        <v>839</v>
+        <v>360</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6">
-        <v>162</v>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -953,48 +959,48 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>598</v>
-      </c>
-      <c r="O11" s="6">
-        <v>3</v>
+        <v>110</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>1709</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>22</v>
+        <v>350</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>10</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
-        <v>1853</v>
+        <v>1709</v>
       </c>
       <c r="C12" s="6">
-        <v>1597</v>
+        <v>842</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="6">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
+      <c r="I12" s="6">
+        <v>52</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1009,48 +1015,48 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>120</v>
-      </c>
-      <c r="O12" s="6">
-        <v>1</v>
+        <v>574</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>1853</v>
+        <v>1709</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
-        <v>128</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
+        <v>1853</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1598</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
+      <c r="E13" s="6">
+        <v>130</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
+      <c r="G13" s="6">
+        <v>5</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
-        <v>15</v>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1065,19 +1071,19 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>77</v>
+        <v>1853</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1085,7 +1091,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="6">
-        <v>400</v>
+        <v>128</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>22</v>
@@ -1105,8 +1111,8 @@
       <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
+      <c r="I14" s="6">
+        <v>15</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>22</v>
@@ -1120,80 +1126,136 @@
       <c r="M14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>22</v>
+      <c r="N14" s="6">
+        <v>36</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>22</v>
+      <c r="P14" s="6">
+        <v>51</v>
       </c>
       <c r="Q14" s="6">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B6:B14)</f>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C6:C14)</f>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D6:D14)</f>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E6:E14)</f>
-      </c>
-      <c r="F15" s="7">
-        <f>SUM(F6:F14)</f>
-      </c>
-      <c r="G15" s="7">
-        <f>SUM(G6:G14)</f>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(H6:H14)</f>
-      </c>
-      <c r="I15" s="7">
-        <f>SUM(I6:I14)</f>
-      </c>
-      <c r="J15" s="7">
-        <f>SUM(J6:J14)</f>
-      </c>
-      <c r="K15" s="7">
-        <f>SUM(K6:K14)</f>
-      </c>
-      <c r="L15" s="7">
-        <f>SUM(L6:L14)</f>
-      </c>
-      <c r="M15" s="7">
-        <f>SUM(M6:M14)</f>
-      </c>
-      <c r="N15" s="7">
-        <f>SUM(N6:N14)</f>
-      </c>
-      <c r="O15" s="7">
-        <f>SUM(O6:O14)</f>
-      </c>
-      <c r="P15" s="7">
-        <f>SUM(P6:P14)</f>
-      </c>
-      <c r="Q15" s="7">
-        <f>SUM(Q6:Q14)</f>
-      </c>
-      <c r="R15" s="7" t="s">
+      <c r="B15" s="6">
+        <v>400</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>400</v>
+      </c>
+      <c r="R15" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="7">
+        <f>SUM(B6:B15)</f>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C6:C15)</f>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D6:D15)</f>
+      </c>
+      <c r="E16" s="7">
+        <f>SUM(E6:E15)</f>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F6:F15)</f>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(G6:G15)</f>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(H6:H15)</f>
+      </c>
+      <c r="I16" s="7">
+        <f>SUM(I6:I15)</f>
+      </c>
+      <c r="J16" s="7">
+        <f>SUM(J6:J15)</f>
+      </c>
+      <c r="K16" s="7">
+        <f>SUM(K6:K15)</f>
+      </c>
+      <c r="L16" s="7">
+        <f>SUM(L6:L15)</f>
+      </c>
+      <c r="M16" s="7">
+        <f>SUM(M6:M15)</f>
+      </c>
+      <c r="N16" s="7">
+        <f>SUM(N6:N15)</f>
+      </c>
+      <c r="O16" s="7">
+        <f>SUM(O6:O15)</f>
+      </c>
+      <c r="P16" s="7">
+        <f>SUM(P6:P15)</f>
+      </c>
+      <c r="Q16" s="7">
+        <f>SUM(Q6:Q15)</f>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,27 +82,21 @@
     <t>-</t>
   </si>
   <si>
-    <t>0.82%</t>
+    <t>8.22%</t>
   </si>
   <si>
     <t>Jardin Derecho</t>
   </si>
   <si>
-    <t>99.27%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Jardin Izquierdo</t>
   </si>
   <si>
-    <t>95.84%</t>
-  </si>
-  <si>
     <t>Oro</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Palcos Dorados</t>
   </si>
   <si>
@@ -133,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>54.83%</t>
+    <t>58.44%</t>
   </si>
 </sst>
 </file>
@@ -646,13 +640,13 @@
         <v>5500</v>
       </c>
       <c r="C6" s="6">
-        <v>45</v>
+        <v>440</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
+      <c r="E6" s="6">
+        <v>8</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -681,14 +675,14 @@
       <c r="N6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>45</v>
+        <v>452</v>
       </c>
       <c r="Q6" s="6">
-        <v>5455</v>
+        <v>5048</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -702,13 +696,13 @@
         <v>1515</v>
       </c>
       <c r="C7" s="6">
-        <v>1187</v>
+        <v>1198</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -735,16 +729,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1504</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>11</v>
+        <v>1515</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,13 +752,13 @@
         <v>1516</v>
       </c>
       <c r="C8" s="6">
-        <v>1141</v>
+        <v>1205</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -791,24 +785,24 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>166</v>
-      </c>
-      <c r="O8" s="6">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1453</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>63</v>
+        <v>1516</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
         <v>174</v>
@@ -820,7 +814,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -832,7 +826,7 @@
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -847,7 +841,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
@@ -859,12 +853,12 @@
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>164</v>
@@ -915,12 +909,12 @@
         <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6">
         <v>360</v>
@@ -971,36 +965,36 @@
         <v>10</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>1709</v>
       </c>
       <c r="C12" s="6">
-        <v>842</v>
+        <v>861</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="6">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1015,7 +1009,7 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>574</v>
+        <v>512</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
@@ -1027,12 +1021,12 @@
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6">
         <v>1853</v>
@@ -1083,12 +1077,12 @@
         <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6">
         <v>128</v>
@@ -1139,12 +1133,12 @@
         <v>77</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
         <v>400</v>
@@ -1195,12 +1189,12 @@
         <v>400</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="7">
         <f>SUM(B6:B15)</f>
@@ -1251,7 +1245,7 @@
         <f>SUM(Q6:Q15)</f>
       </c>
       <c r="R16" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Dorados 2026.xlsx
+++ b/data/asistencia/Dorados 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>8.22%</t>
+    <t>29.58%</t>
   </si>
   <si>
     <t>Jardin Derecho</t>
@@ -103,15 +103,21 @@
     <t>Palcos Morados</t>
   </si>
   <si>
-    <t>97.22%</t>
+    <t>95.00%</t>
   </si>
   <si>
     <t>Plata</t>
   </si>
   <si>
+    <t>99.88%</t>
+  </si>
+  <si>
     <t>Preferente</t>
   </si>
   <si>
+    <t>99.89%</t>
+  </si>
+  <si>
     <t>Suite Premier</t>
   </si>
   <si>
@@ -127,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>58.44%</t>
+    <t>67.17%</t>
   </si>
 </sst>
 </file>
@@ -640,13 +646,13 @@
         <v>5500</v>
       </c>
       <c r="C6" s="6">
-        <v>440</v>
+        <v>1333</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>8</v>
+        <v>294</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -675,14 +681,14 @@
       <c r="N6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="6">
-        <v>4</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>452</v>
+        <v>1627</v>
       </c>
       <c r="Q6" s="6">
-        <v>5048</v>
+        <v>3873</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -696,13 +702,13 @@
         <v>1515</v>
       </c>
       <c r="C7" s="6">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -729,7 +735,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -758,7 +764,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -785,7 +791,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
@@ -807,14 +813,14 @@
       <c r="B9" s="6">
         <v>174</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="C9" s="6">
+        <v>9</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -841,7 +847,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
@@ -876,13 +882,13 @@
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -897,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
@@ -919,14 +925,14 @@
       <c r="B11" s="6">
         <v>360</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
+      <c r="C11" s="6">
+        <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>20</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -938,7 +944,7 @@
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -953,16 +959,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="Q11" s="6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>30</v>
@@ -976,13 +982,13 @@
         <v>1709</v>
       </c>
       <c r="C12" s="6">
-        <v>861</v>
+        <v>1045</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>228</v>
+        <v>443</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1009,36 +1015,36 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>512</v>
+        <v>111</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>1709</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>22</v>
+        <v>1707</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>2</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>1853</v>
       </c>
       <c r="C13" s="6">
-        <v>1598</v>
+        <v>1637</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1065,24 +1071,24 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>1853</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>22</v>
+        <v>1851</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>2</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6">
         <v>128</v>
@@ -1133,12 +1139,12 @@
         <v>77</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6">
         <v>400</v>
@@ -1189,12 +1195,12 @@
         <v>400</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="7">
         <f>SUM(B6:B15)</f>
@@ -1245,7 +1251,7 @@
         <f>SUM(Q6:Q15)</f>
       </c>
       <c r="R16" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
